--- a/research/traditional_assets/database/data/turkey/turkey_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ12"/>
+  <dimension ref="A1:AQ14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.108</v>
+        <v>0.303</v>
       </c>
       <c r="E2">
-        <v>0.23</v>
+        <v>0.441</v>
       </c>
       <c r="G2">
-        <v>0.03463342931357349</v>
+        <v>0.07915486633971125</v>
       </c>
       <c r="H2">
-        <v>0.03463342931357349</v>
+        <v>0.07777163777025625</v>
       </c>
       <c r="I2">
-        <v>0.06159515131989609</v>
+        <v>0.1004179042619327</v>
       </c>
       <c r="J2">
-        <v>0.05025981077593426</v>
+        <v>0.07855431069798668</v>
       </c>
       <c r="K2">
-        <v>282.14</v>
+        <v>358.53</v>
       </c>
       <c r="L2">
-        <v>0.5681090550309082</v>
+        <v>0.6191372521931339</v>
       </c>
       <c r="M2">
-        <v>8.279999999999999</v>
+        <v>3.973</v>
       </c>
       <c r="N2">
-        <v>0.002080140685843487</v>
+        <v>0.0008722091721367258</v>
       </c>
       <c r="O2">
-        <v>0.02934713262919118</v>
+        <v>0.01108135999776867</v>
       </c>
       <c r="P2">
-        <v>8.279999999999999</v>
+        <v>3.466</v>
       </c>
       <c r="Q2">
-        <v>0.002080140685843487</v>
+        <v>0.0007609053588285658</v>
       </c>
       <c r="R2">
-        <v>0.02934713262919118</v>
+        <v>0.009667252391710597</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.5069999999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1276113767933551</v>
       </c>
       <c r="U2">
-        <v>1004.751</v>
+        <v>1110.71</v>
       </c>
       <c r="V2">
-        <v>0.2524182891596533</v>
+        <v>0.2438387741213145</v>
       </c>
       <c r="W2">
-        <v>0.1555890698381027</v>
+        <v>0.2468841447193403</v>
       </c>
       <c r="X2">
-        <v>0.09837717058152493</v>
+        <v>0.1015980734033342</v>
       </c>
       <c r="Y2">
-        <v>0.0572118992565778</v>
+        <v>0.1452860713160061</v>
       </c>
       <c r="Z2">
-        <v>0.03804404446732362</v>
+        <v>0.04277618536268197</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06696694596663437</v>
+        <v>0.1037813679930933</v>
       </c>
       <c r="AC2">
-        <v>-0.06696694596663437</v>
+        <v>-0.09747571480964154</v>
       </c>
       <c r="AD2">
-        <v>12819.5</v>
+        <v>11934.437</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>12819.5</v>
+        <v>11934.437</v>
       </c>
       <c r="AG2">
-        <v>11814.749</v>
+        <v>10823.727</v>
       </c>
       <c r="AH2">
-        <v>0.7630654761904762</v>
+        <v>0.7237581625245147</v>
       </c>
       <c r="AI2">
-        <v>0.8804601648351649</v>
+        <v>0.9031054900431611</v>
       </c>
       <c r="AJ2">
-        <v>0.7479938429587276</v>
+        <v>0.7038070588868709</v>
       </c>
       <c r="AK2">
-        <v>0.8715995552719098</v>
+        <v>0.8942142039066349</v>
       </c>
       <c r="AL2">
-        <v>29.89</v>
+        <v>29.72</v>
       </c>
       <c r="AM2">
-        <v>22.253</v>
+        <v>19.592</v>
       </c>
       <c r="AN2">
-        <v>417.1656361861373</v>
+        <v>203.6245862480805</v>
       </c>
       <c r="AO2">
-        <v>1.023419203747072</v>
+        <v>1.956594885598923</v>
       </c>
       <c r="AP2">
-        <v>384.4695411649853</v>
+        <v>184.6737246203719</v>
       </c>
       <c r="AQ2">
-        <v>1.374646115130544</v>
+        <v>2.968048182931808</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ulusal Faktoring A.S. (IBSE:ULUFA)</t>
+          <t>Gelecek Varlik Yönetimi Anonim Sirketi (IBSE:GLCVY)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,112 +722,100 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.4519774011299435</v>
+        <v>0.340122199592668</v>
       </c>
       <c r="H3">
-        <v>0.4519774011299435</v>
+        <v>0.340122199592668</v>
       </c>
       <c r="I3">
-        <v>0.7457627118644068</v>
+        <v>0.4215885947046843</v>
       </c>
       <c r="J3">
-        <v>0.6009970089730808</v>
+        <v>0.3070156942614113</v>
       </c>
       <c r="K3">
-        <v>2.05</v>
+        <v>18.5</v>
       </c>
       <c r="L3">
-        <v>0.05790960451977401</v>
+        <v>0.3767820773930753</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>2.35</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.009878100042034469</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.127027027027027</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>2.35</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.009878100042034469</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.127027027027027</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="V3">
-        <v>0.04701492537313433</v>
-      </c>
-      <c r="W3">
-        <v>0.0850622406639004</v>
+        <v>0.00474989491382934</v>
       </c>
       <c r="X3">
-        <v>0.1112111553248929</v>
-      </c>
-      <c r="Y3">
-        <v>-0.02614891466099253</v>
-      </c>
-      <c r="Z3">
-        <v>0.3155080213903744</v>
-      </c>
-      <c r="AA3">
-        <v>0.1896193771626297</v>
+        <v>0.06722394643682533</v>
       </c>
       <c r="AB3">
-        <v>0.0701083248783996</v>
-      </c>
-      <c r="AC3">
-        <v>0.1195110522842301</v>
+        <v>0.06948842565256087</v>
       </c>
       <c r="AD3">
-        <v>140.5</v>
+        <v>15.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>140.5</v>
+        <v>15.8</v>
       </c>
       <c r="AG3">
-        <v>139.24</v>
+        <v>14.67</v>
       </c>
       <c r="AH3">
-        <v>0.8398087268380154</v>
+        <v>0.06227828143476547</v>
       </c>
       <c r="AI3">
-        <v>0.8726708074534162</v>
+        <v>0.224113475177305</v>
       </c>
       <c r="AJ3">
-        <v>0.8385931100939532</v>
+        <v>0.05808290770875402</v>
       </c>
       <c r="AK3">
-        <v>0.8716664579942407</v>
+        <v>0.2114747008793427</v>
       </c>
       <c r="AL3">
-        <v>24.2</v>
+        <v>3.97</v>
       </c>
       <c r="AM3">
-        <v>23.91</v>
+        <v>3.97</v>
       </c>
       <c r="AN3">
-        <v>5.30188679245283</v>
+        <v>0.7523809523809524</v>
       </c>
       <c r="AO3">
-        <v>1.090909090909091</v>
+        <v>5.214105793450881</v>
       </c>
       <c r="AP3">
-        <v>5.25433962264151</v>
+        <v>0.6985714285714286</v>
       </c>
       <c r="AQ3">
-        <v>1.104140526976161</v>
+        <v>5.214105793450881</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Creditwest Faktoring Anonim Sirketi (IBSE:CRDFA)</t>
+          <t>Matriks Bilgi Dagitim Hizmetleri A.S. (IBSE:MTRKS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -846,119 +834,113 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.09470000000000001</v>
-      </c>
-      <c r="E4">
-        <v>-0.09970000000000001</v>
-      </c>
       <c r="G4">
-        <v>0.5937834941050375</v>
+        <v>0.2250862068965518</v>
       </c>
       <c r="H4">
-        <v>0.5937834941050375</v>
+        <v>0.1560344827586207</v>
       </c>
       <c r="I4">
-        <v>0.6763129689174705</v>
+        <v>0.2060344827586207</v>
       </c>
       <c r="J4">
-        <v>0.5983824897579447</v>
+        <v>0.2060344827586207</v>
       </c>
       <c r="K4">
-        <v>1.74</v>
+        <v>2.54</v>
       </c>
       <c r="L4">
-        <v>0.1864951768488746</v>
+        <v>0.2189655172413793</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>1.134</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.01766355140186916</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.4464566929133858</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.695</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.01082554517133956</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.2736220472440944</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.4389999999999999</v>
+      </c>
+      <c r="T4">
+        <v>0.3871252204585538</v>
       </c>
       <c r="U4">
-        <v>0.301</v>
+        <v>1.45</v>
       </c>
       <c r="V4">
-        <v>0.01681564245810056</v>
+        <v>0.02258566978193146</v>
       </c>
       <c r="W4">
-        <v>0.08285714285714285</v>
+        <v>0.4551971326164875</v>
       </c>
       <c r="X4">
-        <v>0.0626319128882015</v>
+        <v>0.06585308859145653</v>
       </c>
       <c r="Y4">
-        <v>0.02022522996894136</v>
+        <v>0.389344044025031</v>
       </c>
       <c r="Z4">
-        <v>0.191031941031941</v>
+        <v>3.389830508474577</v>
       </c>
       <c r="AA4">
-        <v>0.1143101684979858</v>
+        <v>0.6984219754529516</v>
       </c>
       <c r="AB4">
-        <v>0.06077676463951201</v>
+        <v>0.06587482164313894</v>
       </c>
       <c r="AC4">
-        <v>0.05353340385847374</v>
+        <v>0.6325471538098126</v>
       </c>
       <c r="AD4">
-        <v>35.1</v>
+        <v>0.037</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>35.1</v>
+        <v>0.037</v>
       </c>
       <c r="AG4">
-        <v>34.799</v>
+        <v>-1.413</v>
       </c>
       <c r="AH4">
-        <v>0.6622641509433963</v>
+        <v>0.0005759920295156996</v>
       </c>
       <c r="AI4">
-        <v>0.6370235934664247</v>
+        <v>0.009053095179838513</v>
       </c>
       <c r="AJ4">
-        <v>0.6603351107231636</v>
+        <v>-0.02250465860767356</v>
       </c>
       <c r="AK4">
-        <v>0.6350298363108816</v>
+        <v>-0.5358361774744028</v>
       </c>
       <c r="AL4">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>5.642</v>
+        <v>-0.149</v>
       </c>
       <c r="AN4">
-        <v>5.580286168521463</v>
-      </c>
-      <c r="AO4">
-        <v>1.10896309314587</v>
+        <v>0.01548117154811715</v>
       </c>
       <c r="AP4">
-        <v>5.532432432432432</v>
+        <v>-0.5912133891213389</v>
       </c>
       <c r="AQ4">
-        <v>1.118397731300957</v>
+        <v>-16.04026845637584</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Türkiye Kalkinma ve Yatirim Bankasi A.S. (IBSE:KLNMA)</t>
+          <t>Ulusal Faktoring A.S. (IBSE:ULUFA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -977,107 +959,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.481</v>
-      </c>
-      <c r="E5">
-        <v>0.634</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.6057971014492753</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.6057971014492753</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.7507246376811594</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.5515887596108049</v>
       </c>
       <c r="K5">
-        <v>92.40000000000001</v>
+        <v>3.13</v>
       </c>
       <c r="L5">
-        <v>0.672</v>
+        <v>0.09072463768115942</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>0.198</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.002675675675675676</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.06325878594249201</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>0.198</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.002675675675675676</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.06325878594249201</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>439.1</v>
+        <v>1.49</v>
       </c>
       <c r="V5">
-        <v>0.1706170345041965</v>
+        <v>0.02013513513513513</v>
       </c>
       <c r="W5">
-        <v>0.2671292281006071</v>
+        <v>0.1526829268292683</v>
       </c>
       <c r="X5">
-        <v>0.05260931695864434</v>
+        <v>0.09423167365207782</v>
       </c>
       <c r="Y5">
-        <v>0.2145199111419628</v>
+        <v>0.05845125317719047</v>
       </c>
       <c r="Z5">
-        <v>0.04643544628685286</v>
+        <v>0.2159759609365218</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.1191299123987277</v>
       </c>
       <c r="AB5">
-        <v>0.05666875260475897</v>
+        <v>0.1013154014536569</v>
       </c>
       <c r="AC5">
-        <v>-0.05666875260475897</v>
+        <v>0.01781451094507089</v>
       </c>
       <c r="AD5">
-        <v>3304.1</v>
+        <v>100.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>3304.1</v>
+        <v>100.9</v>
       </c>
       <c r="AG5">
-        <v>2865</v>
+        <v>99.41000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.5621416540483523</v>
+        <v>0.5769010863350487</v>
       </c>
       <c r="AI5">
-        <v>0.8741930363001376</v>
+        <v>0.8565365025466892</v>
       </c>
       <c r="AJ5">
-        <v>0.5267899827161402</v>
+        <v>0.5732656709532322</v>
       </c>
       <c r="AK5">
-        <v>0.8576560395150427</v>
+        <v>0.8546986501590578</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>21.8</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>21.563</v>
+      </c>
+      <c r="AN5">
+        <v>3.880769230769231</v>
+      </c>
+      <c r="AO5">
+        <v>1.188073394495413</v>
+      </c>
+      <c r="AP5">
+        <v>3.823461538461539</v>
+      </c>
+      <c r="AQ5">
+        <v>1.201131567963641</v>
       </c>
     </row>
     <row r="6">
@@ -1088,7 +1079,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>QNB Finans Finansal Kiralama AS (IBSE:QNBFL)</t>
+          <t>Creditwest Faktoring Anonim Sirketi (IBSE:CRDFA)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1097,28 +1088,28 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.04019999999999999</v>
+        <v>0.00745</v>
       </c>
       <c r="E6">
-        <v>0.217</v>
+        <v>-0.0225</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.7459677419354838</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.7459677419354838</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.7809139784946235</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>0.5609642425399248</v>
       </c>
       <c r="K6">
-        <v>18.3</v>
+        <v>1.22</v>
       </c>
       <c r="L6">
-        <v>1.759615384615385</v>
+        <v>0.1639784946236559</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1142,61 +1133,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>92.40000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="V6">
-        <v>0.130970942593905</v>
+        <v>0.1340996168582375</v>
       </c>
       <c r="W6">
-        <v>0.1406610299769408</v>
+        <v>0.061</v>
       </c>
       <c r="X6">
-        <v>0.05222214982727981</v>
+        <v>0.08219524886025945</v>
       </c>
       <c r="Y6">
-        <v>0.08843888014966102</v>
+        <v>-0.02119524886025945</v>
       </c>
       <c r="Z6">
-        <v>0.01144114411441144</v>
+        <v>0.1357689008923521</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.0761614986495564</v>
       </c>
       <c r="AB6">
-        <v>0.05781842348473025</v>
+        <v>0.09289191761970944</v>
       </c>
       <c r="AC6">
-        <v>-0.05781842348473025</v>
+        <v>-0.01673041897015304</v>
       </c>
       <c r="AD6">
-        <v>887.3</v>
+        <v>20.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>887.3</v>
+        <v>20.5</v>
       </c>
       <c r="AG6">
-        <v>794.9</v>
+        <v>17</v>
       </c>
       <c r="AH6">
-        <v>0.557069311903566</v>
+        <v>0.4399141630901288</v>
       </c>
       <c r="AI6">
-        <v>0.8710975849204792</v>
+        <v>0.6065088757396451</v>
       </c>
       <c r="AJ6">
-        <v>0.5297920554518795</v>
+        <v>0.394431554524362</v>
       </c>
       <c r="AK6">
-        <v>0.8582379615633772</v>
+        <v>0.5610561056105611</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>3.906</v>
+      </c>
+      <c r="AN6">
+        <v>3.528399311531842</v>
+      </c>
+      <c r="AO6">
+        <v>1.470886075949367</v>
+      </c>
+      <c r="AP6">
+        <v>2.925989672977625</v>
+      </c>
+      <c r="AQ6">
+        <v>1.487455197132616</v>
       </c>
     </row>
     <row r="7">
@@ -1207,7 +1210,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Seker Finansal Kiralama A.S. (IBSE:SEKFK)</t>
+          <t>Lider Faktoring A.S. (IBSE:LIDFA)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1216,28 +1219,28 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.108</v>
+        <v>0.187</v>
       </c>
       <c r="E7">
-        <v>0.374</v>
+        <v>0.399</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.003408071748878924</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.003408071748878924</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>0.1502242152466368</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>0.1107837853394101</v>
       </c>
       <c r="K7">
-        <v>1.87</v>
+        <v>6.32</v>
       </c>
       <c r="L7">
-        <v>1.7</v>
+        <v>0.2834080717488789</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1261,64 +1264,70 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>1.34</v>
+        <v>2.26</v>
       </c>
       <c r="V7">
-        <v>0.06871794871794872</v>
+        <v>0.04913043478260869</v>
       </c>
       <c r="W7">
-        <v>0.1640350877192983</v>
+        <v>0.2821428571428572</v>
       </c>
       <c r="X7">
-        <v>0.09304521220039927</v>
+        <v>0.1023694843077783</v>
       </c>
       <c r="Y7">
-        <v>0.07098987551889899</v>
+        <v>0.1797733728350789</v>
       </c>
       <c r="Z7">
-        <v>0.01246882793017456</v>
+        <v>0.1854161470025776</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>0.02054110262799405</v>
       </c>
       <c r="AB7">
-        <v>0.0664532189424774</v>
+        <v>0.1050071188420382</v>
       </c>
       <c r="AC7">
-        <v>-0.0664532189424774</v>
+        <v>-0.08446601621404416</v>
       </c>
       <c r="AD7">
-        <v>78.3</v>
+        <v>80.7</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>78.3</v>
+        <v>80.7</v>
       </c>
       <c r="AG7">
-        <v>76.95999999999999</v>
+        <v>78.44</v>
       </c>
       <c r="AH7">
-        <v>0.8006134969325154</v>
+        <v>0.6369376479873717</v>
       </c>
       <c r="AI7">
-        <v>0.841031149301826</v>
+        <v>0.8061938061938063</v>
       </c>
       <c r="AJ7">
-        <v>0.7978436657681941</v>
+        <v>0.6303439408550305</v>
       </c>
       <c r="AK7">
-        <v>0.8387096774193549</v>
+        <v>0.8017170891251022</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.286</v>
+        <v>-5.14</v>
+      </c>
+      <c r="AN7">
+        <v>23.66568914956012</v>
+      </c>
+      <c r="AP7">
+        <v>23.00293255131965</v>
       </c>
       <c r="AQ7">
-        <v>-0</v>
+        <v>-0.6517509727626459</v>
       </c>
     </row>
     <row r="8">
@@ -1329,7 +1338,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Garanti Faktoring A.S. (IBSE:GARFA)</t>
+          <t>QNB Finans Finansal Kiralama AS (IBSE:QNBFL)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1338,10 +1347,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.9379999999999999</v>
+        <v>-0.139</v>
       </c>
       <c r="E8">
-        <v>0.369</v>
+        <v>0.311</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1356,10 +1365,10 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>12.5</v>
+        <v>19.3</v>
       </c>
       <c r="L8">
-        <v>0.7183908045977012</v>
+        <v>8.247863247863249</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1383,64 +1392,61 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>4.52</v>
+        <v>22.3</v>
       </c>
       <c r="V8">
-        <v>0.05478787878787878</v>
+        <v>0.02914651679519017</v>
       </c>
       <c r="W8">
-        <v>0.4826254826254827</v>
+        <v>0.146991622239147</v>
       </c>
       <c r="X8">
-        <v>0.1037091289626506</v>
+        <v>0.08311398594257742</v>
       </c>
       <c r="Y8">
-        <v>0.3789163536628321</v>
+        <v>0.06387763629656958</v>
       </c>
       <c r="Z8">
-        <v>0.04963770183146003</v>
+        <v>0.002526452170157633</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06748067299079134</v>
+        <v>0.09239581247513468</v>
       </c>
       <c r="AC8">
-        <v>-0.06748067299079134</v>
+        <v>-0.09239581247513468</v>
       </c>
       <c r="AD8">
-        <v>390.7</v>
+        <v>634.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>390.7</v>
+        <v>634.7</v>
       </c>
       <c r="AG8">
-        <v>386.18</v>
+        <v>612.4000000000001</v>
       </c>
       <c r="AH8">
-        <v>0.8256551141166526</v>
+        <v>0.4534219174167738</v>
       </c>
       <c r="AI8">
-        <v>0.9182138660399529</v>
+        <v>0.8853396568559073</v>
       </c>
       <c r="AJ8">
-        <v>0.823973713407869</v>
+        <v>0.4445735027223231</v>
       </c>
       <c r="AK8">
-        <v>0.9173357404152216</v>
+        <v>0.8816585084940973</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-0.763</v>
-      </c>
-      <c r="AQ8">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1451,7 +1457,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Is Finansal Kiralama Anonim Sirketi (IBSE:ISFIN)</t>
+          <t>Seker Finansal Kiralama A.S. (IBSE:SEKFK)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1459,11 +1465,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D9">
-        <v>-0.0311</v>
-      </c>
       <c r="E9">
-        <v>0.23</v>
+        <v>0.608</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1478,88 +1481,94 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>35.1</v>
+        <v>5.22</v>
       </c>
       <c r="L9">
-        <v>0.7834821428571429</v>
+        <v>3.48</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>0.209</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.006551724137931035</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.04003831417624521</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>0.209</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.006551724137931035</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.04003831417624521</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>65.90000000000001</v>
+        <v>2.67</v>
       </c>
       <c r="V9">
-        <v>0.4035517452541335</v>
+        <v>0.08369905956112852</v>
       </c>
       <c r="W9">
-        <v>0.1906572514937534</v>
+        <v>0.3527027027027027</v>
       </c>
       <c r="X9">
-        <v>0.1596454720002882</v>
+        <v>0.1008266624988901</v>
       </c>
       <c r="Y9">
-        <v>0.03101177949346523</v>
+        <v>0.2518760402038125</v>
       </c>
       <c r="Z9">
-        <v>0.03233774464442195</v>
+        <v>0.01634699215344377</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.07032161908721883</v>
+        <v>0.1025556171441484</v>
       </c>
       <c r="AC9">
-        <v>-0.07032161908721883</v>
+        <v>-0.1025556171441484</v>
       </c>
       <c r="AD9">
-        <v>1390.4</v>
+        <v>53.6</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1390.4</v>
+        <v>53.6</v>
       </c>
       <c r="AG9">
-        <v>1324.5</v>
+        <v>50.93</v>
       </c>
       <c r="AH9">
-        <v>0.8948960545793911</v>
+        <v>0.6269005847953216</v>
       </c>
       <c r="AI9">
-        <v>0.8664547890571447</v>
+        <v>0.8145896656534954</v>
       </c>
       <c r="AJ9">
-        <v>0.89024062373975</v>
+        <v>0.6148738379814077</v>
       </c>
       <c r="AK9">
-        <v>0.860735638159605</v>
+        <v>0.8067479803579914</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>-0.133</v>
+      </c>
+      <c r="AQ9">
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -1570,7 +1579,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vakif Finansal Kiralama A.S. (IBSE:VAKFN)</t>
+          <t>Türkiye Kalkinma ve Yatirim Bankasi A.S. (IBSE:KLNMA)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1579,10 +1588,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.287</v>
+        <v>0.546</v>
       </c>
       <c r="E10">
-        <v>0.241</v>
+        <v>0.601</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1597,10 +1606,10 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>7.97</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="L10">
-        <v>0.7116071428571429</v>
+        <v>0.604201680672269</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1624,64 +1633,61 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>43.5</v>
+        <v>585.3</v>
       </c>
       <c r="V10">
-        <v>0.7435897435897436</v>
+        <v>0.2826443886420706</v>
       </c>
       <c r="W10">
-        <v>0.1840646651270208</v>
+        <v>0.1512092534174553</v>
       </c>
       <c r="X10">
-        <v>0.1431234769336482</v>
+        <v>0.1049173550335042</v>
       </c>
       <c r="Y10">
-        <v>0.04094118819337259</v>
+        <v>0.04629189838395116</v>
       </c>
       <c r="Z10">
-        <v>0.02496099843993759</v>
+        <v>0.0356234096692112</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.0718956726161251</v>
+        <v>0.1059567601790008</v>
       </c>
       <c r="AC10">
-        <v>-0.0718956726161251</v>
+        <v>-0.1059567601790008</v>
       </c>
       <c r="AD10">
-        <v>432.8</v>
+        <v>3886.3</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>432.8</v>
+        <v>3886.3</v>
       </c>
       <c r="AG10">
-        <v>389.3</v>
+        <v>3301</v>
       </c>
       <c r="AH10">
-        <v>0.8809281498066355</v>
+        <v>0.6523811921908311</v>
       </c>
       <c r="AI10">
-        <v>0.9022305607671461</v>
+        <v>0.926015059092642</v>
       </c>
       <c r="AJ10">
-        <v>0.8693613220187584</v>
+        <v>0.6145053799471313</v>
       </c>
       <c r="AK10">
-        <v>0.8924805135259056</v>
+        <v>0.9140246434999307</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1.14</v>
-      </c>
-      <c r="AQ10">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1692,7 +1698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Türkiye Sinai Kalkinma Bankasi A.S. (IBSE:TSKB)</t>
+          <t>Garanti Faktoring A.S. (IBSE:GARFA)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1701,10 +1707,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.204</v>
+        <v>0.679</v>
       </c>
       <c r="E11">
-        <v>0.142</v>
+        <v>0.599</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1719,91 +1725,91 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>107.9</v>
+        <v>14.6</v>
       </c>
       <c r="L11">
-        <v>0.5185007208073042</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="M11">
-        <v>8.279999999999999</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.02711198428290766</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>0.07673772011121407</v>
+        <v>-0</v>
       </c>
       <c r="P11">
-        <v>8.279999999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.02711198428290766</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.07673772011121407</v>
+        <v>-0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>354.7</v>
+        <v>6.21</v>
       </c>
       <c r="V11">
-        <v>1.161427635887361</v>
+        <v>0.05452151009657594</v>
       </c>
       <c r="W11">
-        <v>0.1471430519569072</v>
+        <v>0.4195402298850575</v>
       </c>
       <c r="X11">
-        <v>0.3273779843712138</v>
+        <v>0.1152170717249814</v>
       </c>
       <c r="Y11">
-        <v>-0.1802349324143066</v>
+        <v>0.3043231581600761</v>
       </c>
       <c r="Z11">
-        <v>0.03148989100351519</v>
+        <v>0.05202147370421397</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.07266569968110524</v>
+        <v>0.1070349630124192</v>
       </c>
       <c r="AC11">
-        <v>-0.07266569968110524</v>
+        <v>-0.1070349630124192</v>
       </c>
       <c r="AD11">
-        <v>6060.7</v>
+        <v>270.1</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>6060.7</v>
+        <v>270.1</v>
       </c>
       <c r="AG11">
-        <v>5706</v>
+        <v>263.89</v>
       </c>
       <c r="AH11">
-        <v>0.9520271437771949</v>
+        <v>0.7033854166666668</v>
       </c>
       <c r="AI11">
-        <v>0.8885744864896565</v>
+        <v>0.8961512939615129</v>
       </c>
       <c r="AJ11">
-        <v>0.9491965265994611</v>
+        <v>0.698509754096191</v>
       </c>
       <c r="AK11">
-        <v>0.8824621094958243</v>
+        <v>0.8939665977844777</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>-0.465</v>
+      </c>
+      <c r="AQ11">
+        <v>-0</v>
       </c>
     </row>
     <row r="12">
@@ -1814,7 +1820,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lider Faktoring A.S. (IBSE:LIDFA)</t>
+          <t>Vakif Finansal Kiralama A.S. (IBSE:VAKFN)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1823,37 +1829,37 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0574</v>
+        <v>0.608</v>
       </c>
       <c r="E12">
-        <v>0.008100000000000001</v>
+        <v>0.635</v>
       </c>
       <c r="G12">
-        <v>-0.202803738317757</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>-0.202803738317757</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>-0.09906542056074767</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>-0.07612568696246158</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>2.31</v>
+        <v>18.8</v>
       </c>
       <c r="L12">
-        <v>0.1079439252336449</v>
+        <v>1.413533834586466</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>0.068</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.0003992953611274222</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0.003617021276595745</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1865,73 +1871,311 @@
         <v>-0</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>0.068</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
       </c>
       <c r="U12">
-        <v>1.73</v>
+        <v>62.8</v>
       </c>
       <c r="V12">
-        <v>0.06290909090909091</v>
+        <v>0.368761009982384</v>
       </c>
       <c r="W12">
-        <v>0.1008733624454149</v>
+        <v>0.4008528784648188</v>
       </c>
       <c r="X12">
-        <v>0.08721911944173205</v>
+        <v>0.1208356444596767</v>
       </c>
       <c r="Y12">
-        <v>0.0136542430036828</v>
+        <v>0.2800172340051421</v>
       </c>
       <c r="Z12">
-        <v>0.1510957975598735</v>
+        <v>0.03049060064190738</v>
       </c>
       <c r="AA12">
-        <v>-0.01150227138638639</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.06575659084566444</v>
+        <v>0.110444734036115</v>
       </c>
       <c r="AC12">
-        <v>-0.07725886223205083</v>
+        <v>-0.110444734036115</v>
       </c>
       <c r="AD12">
-        <v>99.59999999999999</v>
+        <v>449.8</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>99.59999999999999</v>
+        <v>449.8</v>
       </c>
       <c r="AG12">
-        <v>97.86999999999999</v>
+        <v>387</v>
       </c>
       <c r="AH12">
-        <v>0.7836349331235247</v>
+        <v>0.7253668763102725</v>
       </c>
       <c r="AI12">
-        <v>0.8163934426229508</v>
+        <v>0.8913991280221958</v>
       </c>
       <c r="AJ12">
-        <v>0.7806492781367153</v>
+        <v>0.6944195226987261</v>
       </c>
       <c r="AK12">
-        <v>0.8137523904548101</v>
+        <v>0.8759619737437755</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-5.11</v>
-      </c>
-      <c r="AN12">
-        <v>-48.34951456310679</v>
-      </c>
-      <c r="AP12">
-        <v>-47.50970873786407</v>
+        <v>-3.96</v>
       </c>
       <c r="AQ12">
-        <v>0.4148727984344422</v>
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Is Finansal Kiralama Anonim Sirketi (IBSE:ISFIN)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.07400000000000001</v>
+      </c>
+      <c r="E13">
+        <v>0.441</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>37.9</v>
+      </c>
+      <c r="L13">
+        <v>0.9844155844155844</v>
+      </c>
+      <c r="M13">
+        <v>-0</v>
+      </c>
+      <c r="N13">
+        <v>-0</v>
+      </c>
+      <c r="O13">
+        <v>-0</v>
+      </c>
+      <c r="P13">
+        <v>-0</v>
+      </c>
+      <c r="Q13">
+        <v>-0</v>
+      </c>
+      <c r="R13">
+        <v>-0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>20</v>
+      </c>
+      <c r="V13">
+        <v>0.0664451827242525</v>
+      </c>
+      <c r="W13">
+        <v>0.1881827209533267</v>
+      </c>
+      <c r="X13">
+        <v>0.1501514296051024</v>
+      </c>
+      <c r="Y13">
+        <v>0.03803129134822428</v>
+      </c>
+      <c r="Z13">
+        <v>0.02523132537858457</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.1128072737891261</v>
+      </c>
+      <c r="AC13">
+        <v>-0.1128072737891261</v>
+      </c>
+      <c r="AD13">
+        <v>1218.8</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>1218.8</v>
+      </c>
+      <c r="AG13">
+        <v>1198.8</v>
+      </c>
+      <c r="AH13">
+        <v>0.8019476246874588</v>
+      </c>
+      <c r="AI13">
+        <v>0.8861422131743494</v>
+      </c>
+      <c r="AJ13">
+        <v>0.7993065742098946</v>
+      </c>
+      <c r="AK13">
+        <v>0.8844621513944224</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Türkiye Sinai Kalkinma Bankasi A.S. (IBSE:TSKB)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.419</v>
+      </c>
+      <c r="E14">
+        <v>0.396</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>159.1</v>
+      </c>
+      <c r="L14">
+        <v>0.6176242236024844</v>
+      </c>
+      <c r="M14">
+        <v>0.014</v>
+      </c>
+      <c r="N14">
+        <v>2.141000152928583e-05</v>
+      </c>
+      <c r="O14">
+        <v>8.799497171590195e-05</v>
+      </c>
+      <c r="P14">
+        <v>0.014</v>
+      </c>
+      <c r="Q14">
+        <v>2.141000152928583e-05</v>
+      </c>
+      <c r="R14">
+        <v>8.799497171590195e-05</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>401.6</v>
+      </c>
+      <c r="V14">
+        <v>0.6141611867257991</v>
+      </c>
+      <c r="W14">
+        <v>0.2116254322958234</v>
+      </c>
+      <c r="X14">
+        <v>0.2315226116346315</v>
+      </c>
+      <c r="Y14">
+        <v>-0.01989717933880816</v>
+      </c>
+      <c r="Z14">
+        <v>0.03989044374557021</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.1178678942096615</v>
+      </c>
+      <c r="AC14">
+        <v>-0.1178678942096615</v>
+      </c>
+      <c r="AD14">
+        <v>5203.2</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>5203.2</v>
+      </c>
+      <c r="AG14">
+        <v>4801.599999999999</v>
+      </c>
+      <c r="AH14">
+        <v>0.8883577196906319</v>
+      </c>
+      <c r="AI14">
+        <v>0.9084274665223389</v>
+      </c>
+      <c r="AJ14">
+        <v>0.8801393089542664</v>
+      </c>
+      <c r="AK14">
+        <v>0.9015226901485139</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/turkey/turkey_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ14"/>
+  <dimension ref="A1:AQ15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.303</v>
+        <v>0.7625</v>
       </c>
       <c r="E2">
-        <v>0.441</v>
+        <v>0.7335</v>
       </c>
       <c r="G2">
-        <v>0.07915486633971125</v>
+        <v>0.07519328672447766</v>
       </c>
       <c r="H2">
-        <v>0.07777163777025625</v>
+        <v>0.07444014362728919</v>
       </c>
       <c r="I2">
-        <v>0.1004179042619327</v>
+        <v>0.1043078184855123</v>
       </c>
       <c r="J2">
-        <v>0.07855431069798668</v>
+        <v>0.07731468901415731</v>
       </c>
       <c r="K2">
-        <v>358.53</v>
+        <v>590.4450000000001</v>
       </c>
       <c r="L2">
-        <v>0.6191372521931339</v>
+        <v>0.5905572058691152</v>
       </c>
       <c r="M2">
-        <v>3.973</v>
+        <v>12.324</v>
       </c>
       <c r="N2">
-        <v>0.0008722091721367258</v>
+        <v>0.001624657245306897</v>
       </c>
       <c r="O2">
-        <v>0.01108135999776867</v>
+        <v>0.02087239285623555</v>
       </c>
       <c r="P2">
-        <v>3.466</v>
+        <v>12.06</v>
       </c>
       <c r="Q2">
-        <v>0.0007609053588285658</v>
+        <v>0.001589854461084159</v>
       </c>
       <c r="R2">
-        <v>0.009667252391710597</v>
+        <v>0.02042527246398903</v>
       </c>
       <c r="S2">
-        <v>0.5069999999999999</v>
+        <v>0.264</v>
       </c>
       <c r="T2">
-        <v>0.1276113767933551</v>
+        <v>0.02142161635832522</v>
       </c>
       <c r="U2">
-        <v>1110.71</v>
+        <v>1623.315</v>
       </c>
       <c r="V2">
-        <v>0.2438387741213145</v>
+        <v>0.2139995517823244</v>
       </c>
       <c r="W2">
-        <v>0.2468841447193403</v>
+        <v>0.4483606557377049</v>
       </c>
       <c r="X2">
-        <v>0.1015980734033342</v>
+        <v>0.1127791817857437</v>
       </c>
       <c r="Y2">
-        <v>0.1452860713160061</v>
+        <v>0.3355814739519613</v>
       </c>
       <c r="Z2">
-        <v>0.04277618536268197</v>
+        <v>0.08185983555163791</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1037813679930933</v>
+        <v>0.09957261454558899</v>
       </c>
       <c r="AC2">
-        <v>-0.09747571480964154</v>
+        <v>-0.0806814871428552</v>
       </c>
       <c r="AD2">
-        <v>11934.437</v>
+        <v>12579.12</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11934.437</v>
+        <v>12579.12</v>
       </c>
       <c r="AG2">
-        <v>10823.727</v>
+        <v>10955.805</v>
       </c>
       <c r="AH2">
-        <v>0.7237581625245147</v>
+        <v>0.6238182330327422</v>
       </c>
       <c r="AI2">
-        <v>0.9031054900431611</v>
+        <v>0.8816112327090837</v>
       </c>
       <c r="AJ2">
-        <v>0.7038070588868709</v>
+        <v>0.590883215160879</v>
       </c>
       <c r="AK2">
-        <v>0.8942142039066349</v>
+        <v>0.8664129698541282</v>
       </c>
       <c r="AL2">
-        <v>29.72</v>
+        <v>38.887</v>
       </c>
       <c r="AM2">
-        <v>19.592</v>
+        <v>-2.449999999999996</v>
       </c>
       <c r="AN2">
-        <v>203.6245862480805</v>
+        <v>119.8000019047438</v>
       </c>
       <c r="AO2">
-        <v>1.956594885598923</v>
+        <v>2.681821688482012</v>
       </c>
       <c r="AP2">
-        <v>184.6737246203719</v>
+        <v>104.3400062856544</v>
       </c>
       <c r="AQ2">
-        <v>2.968048182931808</v>
+        <v>-42.56653061224497</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gelecek Varlik Yönetimi Anonim Sirketi (IBSE:GLCVY)</t>
+          <t>Matriks Bilgi Dagitim Hizmetleri A.S. (IBSE:MTRKS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,100 +722,115 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.340122199592668</v>
+        <v>0.2668707482993197</v>
       </c>
       <c r="H3">
-        <v>0.340122199592668</v>
+        <v>0.2156462585034014</v>
       </c>
       <c r="I3">
-        <v>0.4215885947046843</v>
+        <v>0.1993197278911565</v>
       </c>
       <c r="J3">
-        <v>0.3070156942614113</v>
+        <v>0.1993197278911565</v>
       </c>
       <c r="K3">
-        <v>18.5</v>
+        <v>3.23</v>
       </c>
       <c r="L3">
-        <v>0.3767820773930753</v>
+        <v>0.2197278911564626</v>
       </c>
       <c r="M3">
-        <v>2.35</v>
+        <v>0.629</v>
       </c>
       <c r="N3">
-        <v>0.009878100042034469</v>
+        <v>0.009332344213649851</v>
       </c>
       <c r="O3">
-        <v>0.127027027027027</v>
+        <v>0.1947368421052632</v>
       </c>
       <c r="P3">
-        <v>2.35</v>
+        <v>0.365</v>
       </c>
       <c r="Q3">
-        <v>0.009878100042034469</v>
+        <v>0.005415430267062314</v>
       </c>
       <c r="R3">
-        <v>0.127027027027027</v>
+        <v>0.1130030959752322</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.264</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.4197138314785374</v>
       </c>
       <c r="U3">
-        <v>1.13</v>
+        <v>2.03</v>
       </c>
       <c r="V3">
-        <v>0.00474989491382934</v>
+        <v>0.0301186943620178</v>
+      </c>
+      <c r="W3">
+        <v>0.8014888337468982</v>
       </c>
       <c r="X3">
-        <v>0.06722394643682533</v>
+        <v>0.07259136298772458</v>
+      </c>
+      <c r="Y3">
+        <v>0.7288974707591735</v>
+      </c>
+      <c r="Z3">
+        <v>5.617118838364539</v>
+      </c>
+      <c r="AA3">
+        <v>1.119602598395109</v>
       </c>
       <c r="AB3">
-        <v>0.06948842565256087</v>
+        <v>0.07259717400682705</v>
+      </c>
+      <c r="AC3">
+        <v>1.047005424388282</v>
       </c>
       <c r="AD3">
-        <v>15.8</v>
+        <v>0.021</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.8</v>
+        <v>0.021</v>
       </c>
       <c r="AG3">
-        <v>14.67</v>
+        <v>-2.009</v>
       </c>
       <c r="AH3">
-        <v>0.06227828143476547</v>
+        <v>0.0003114756529864582</v>
       </c>
       <c r="AI3">
-        <v>0.224113475177305</v>
+        <v>0.004133044676244834</v>
       </c>
       <c r="AJ3">
-        <v>0.05808290770875402</v>
+        <v>-0.03072288235384074</v>
       </c>
       <c r="AK3">
-        <v>0.2114747008793427</v>
+        <v>-0.6584726319239594</v>
       </c>
       <c r="AL3">
-        <v>3.97</v>
+        <v>0.031</v>
       </c>
       <c r="AM3">
-        <v>3.97</v>
+        <v>-0.3110000000000001</v>
       </c>
       <c r="AN3">
-        <v>0.7523809523809524</v>
+        <v>0.006885245901639345</v>
       </c>
       <c r="AO3">
-        <v>5.214105793450881</v>
+        <v>94.51612903225806</v>
       </c>
       <c r="AP3">
-        <v>0.6985714285714286</v>
+        <v>-0.6586885245901639</v>
       </c>
       <c r="AQ3">
-        <v>5.214105793450881</v>
+        <v>-9.421221864951768</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Matriks Bilgi Dagitim Hizmetleri A.S. (IBSE:MTRKS)</t>
+          <t>Gelecek Varlik Yönetimi Anonim Sirketi (IBSE:GLCVY)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,112 +850,115 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.2250862068965518</v>
+        <v>0.384508990318119</v>
       </c>
       <c r="H4">
-        <v>0.1560344827586207</v>
+        <v>0.384508990318119</v>
       </c>
       <c r="I4">
-        <v>0.2060344827586207</v>
+        <v>0.4923928077455049</v>
       </c>
       <c r="J4">
-        <v>0.2060344827586207</v>
+        <v>0.3510548057879911</v>
       </c>
       <c r="K4">
-        <v>2.54</v>
+        <v>21.5</v>
       </c>
       <c r="L4">
-        <v>0.2189655172413793</v>
+        <v>0.297372060857538</v>
       </c>
       <c r="M4">
-        <v>1.134</v>
+        <v>10.9</v>
       </c>
       <c r="N4">
-        <v>0.01766355140186916</v>
+        <v>0.0675759454432734</v>
       </c>
       <c r="O4">
-        <v>0.4464566929133858</v>
+        <v>0.5069767441860465</v>
       </c>
       <c r="P4">
-        <v>0.695</v>
+        <v>10.9</v>
       </c>
       <c r="Q4">
-        <v>0.01082554517133956</v>
+        <v>0.0675759454432734</v>
       </c>
       <c r="R4">
-        <v>0.2736220472440944</v>
+        <v>0.5069767441860465</v>
       </c>
       <c r="S4">
-        <v>0.4389999999999999</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.3871252204585538</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1.45</v>
+        <v>20.5</v>
       </c>
       <c r="V4">
-        <v>0.02258566978193146</v>
+        <v>0.1270923744575325</v>
       </c>
       <c r="W4">
-        <v>0.4551971326164875</v>
+        <v>0.3930530164533821</v>
       </c>
       <c r="X4">
-        <v>0.06585308859145653</v>
+        <v>0.07641631084637139</v>
       </c>
       <c r="Y4">
-        <v>0.389344044025031</v>
+        <v>0.3166367056070107</v>
       </c>
       <c r="Z4">
-        <v>3.389830508474577</v>
+        <v>1.042237278362404</v>
       </c>
       <c r="AA4">
-        <v>0.6984219754529516</v>
+        <v>0.3658824053405184</v>
       </c>
       <c r="AB4">
-        <v>0.06587482164313894</v>
+        <v>0.07836508738266461</v>
       </c>
       <c r="AC4">
-        <v>0.6325471538098126</v>
+        <v>0.2875173179578537</v>
       </c>
       <c r="AD4">
-        <v>0.037</v>
+        <v>24.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.037</v>
+        <v>24.4</v>
       </c>
       <c r="AG4">
-        <v>-1.413</v>
+        <v>3.899999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.0005759920295156996</v>
+        <v>0.1313947226709747</v>
       </c>
       <c r="AI4">
-        <v>0.009053095179838513</v>
+        <v>0.3403068340306835</v>
       </c>
       <c r="AJ4">
-        <v>-0.02250465860767356</v>
+        <v>0.02360774818401936</v>
       </c>
       <c r="AK4">
-        <v>-0.5358361774744028</v>
+        <v>0.07617187499999997</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AM4">
-        <v>-0.149</v>
+        <v>3.44</v>
       </c>
       <c r="AN4">
-        <v>0.01548117154811715</v>
+        <v>0.6796657381615598</v>
+      </c>
+      <c r="AO4">
+        <v>10.34883720930233</v>
       </c>
       <c r="AP4">
-        <v>-0.5912133891213389</v>
+        <v>0.1086350974930362</v>
       </c>
       <c r="AQ4">
-        <v>-16.04026845637584</v>
+        <v>10.34883720930233</v>
       </c>
     </row>
     <row r="5">
@@ -959,41 +977,47 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.439</v>
+      </c>
+      <c r="E5">
+        <v>0.775</v>
+      </c>
       <c r="G5">
-        <v>0.6057971014492753</v>
+        <v>0.4923076923076923</v>
       </c>
       <c r="H5">
-        <v>0.6057971014492753</v>
+        <v>0.4923076923076923</v>
       </c>
       <c r="I5">
-        <v>0.7507246376811594</v>
+        <v>0.7569230769230769</v>
       </c>
       <c r="J5">
-        <v>0.5515887596108049</v>
+        <v>0.558834697217676</v>
       </c>
       <c r="K5">
-        <v>3.13</v>
+        <v>13.8</v>
       </c>
       <c r="L5">
-        <v>0.09072463768115942</v>
+        <v>0.2123076923076923</v>
       </c>
       <c r="M5">
-        <v>0.198</v>
+        <v>0.407</v>
       </c>
       <c r="N5">
-        <v>0.002675675675675676</v>
+        <v>0.01004938271604938</v>
       </c>
       <c r="O5">
-        <v>0.06325878594249201</v>
+        <v>0.0294927536231884</v>
       </c>
       <c r="P5">
-        <v>0.198</v>
+        <v>0.407</v>
       </c>
       <c r="Q5">
-        <v>0.002675675675675676</v>
+        <v>0.01004938271604938</v>
       </c>
       <c r="R5">
-        <v>0.06325878594249201</v>
+        <v>0.0294927536231884</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1002,73 +1026,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1.49</v>
+        <v>5.68</v>
       </c>
       <c r="V5">
-        <v>0.02013513513513513</v>
+        <v>0.1402469135802469</v>
       </c>
       <c r="W5">
-        <v>0.1526829268292683</v>
+        <v>0.8070175438596491</v>
       </c>
       <c r="X5">
-        <v>0.09423167365207782</v>
+        <v>0.1531007350336396</v>
       </c>
       <c r="Y5">
-        <v>0.05845125317719047</v>
+        <v>0.6539168088260094</v>
       </c>
       <c r="Z5">
-        <v>0.2159759609365218</v>
+        <v>0.5367464905037159</v>
       </c>
       <c r="AA5">
-        <v>0.1191299123987277</v>
+        <v>0.2999525625032943</v>
       </c>
       <c r="AB5">
-        <v>0.1013154014536569</v>
+        <v>0.107575614922178</v>
       </c>
       <c r="AC5">
-        <v>0.01781451094507089</v>
+        <v>0.1923769475811163</v>
       </c>
       <c r="AD5">
-        <v>100.9</v>
+        <v>128.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>100.9</v>
+        <v>128.7</v>
       </c>
       <c r="AG5">
-        <v>99.41000000000001</v>
+        <v>123.02</v>
       </c>
       <c r="AH5">
-        <v>0.5769010863350487</v>
+        <v>0.7606382978723404</v>
       </c>
       <c r="AI5">
-        <v>0.8565365025466892</v>
+        <v>0.8395303326810176</v>
       </c>
       <c r="AJ5">
-        <v>0.5732656709532322</v>
+        <v>0.7523238747553815</v>
       </c>
       <c r="AK5">
-        <v>0.8546986501590578</v>
+        <v>0.833355913832814</v>
       </c>
       <c r="AL5">
-        <v>21.8</v>
+        <v>30.8</v>
       </c>
       <c r="AM5">
-        <v>21.563</v>
+        <v>30.463</v>
       </c>
       <c r="AN5">
-        <v>3.880769230769231</v>
+        <v>2.605263157894737</v>
       </c>
       <c r="AO5">
-        <v>1.188073394495413</v>
+        <v>1.597402597402597</v>
       </c>
       <c r="AP5">
-        <v>3.823461538461539</v>
+        <v>2.490283400809716</v>
       </c>
       <c r="AQ5">
-        <v>1.201131567963641</v>
+        <v>1.61507402422611</v>
       </c>
     </row>
     <row r="6">
@@ -1088,28 +1112,28 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.00745</v>
+        <v>0.116</v>
       </c>
       <c r="E6">
-        <v>-0.0225</v>
+        <v>0.213</v>
       </c>
       <c r="G6">
-        <v>0.7459677419354838</v>
+        <v>0.7185104052573931</v>
       </c>
       <c r="H6">
-        <v>0.7459677419354838</v>
+        <v>0.7185104052573931</v>
       </c>
       <c r="I6">
-        <v>0.7809139784946235</v>
+        <v>0.764512595837897</v>
       </c>
       <c r="J6">
-        <v>0.5609642425399248</v>
+        <v>0.551160243511042</v>
       </c>
       <c r="K6">
-        <v>1.22</v>
+        <v>2.17</v>
       </c>
       <c r="L6">
-        <v>0.1639784946236559</v>
+        <v>0.2376779846659365</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1133,73 +1157,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>3.5</v>
+        <v>1.53</v>
       </c>
       <c r="V6">
-        <v>0.1340996168582375</v>
+        <v>0.08010471204188481</v>
       </c>
       <c r="W6">
-        <v>0.061</v>
+        <v>0.1631578947368421</v>
       </c>
       <c r="X6">
-        <v>0.08219524886025945</v>
+        <v>0.09420665707985598</v>
       </c>
       <c r="Y6">
-        <v>-0.02119524886025945</v>
+        <v>0.0689512376569861</v>
       </c>
       <c r="Z6">
-        <v>0.1357689008923521</v>
+        <v>0.3013201320132013</v>
       </c>
       <c r="AA6">
-        <v>0.0761614986495564</v>
+        <v>0.1660756773351754</v>
       </c>
       <c r="AB6">
-        <v>0.09289191761970944</v>
+        <v>0.09376594518244211</v>
       </c>
       <c r="AC6">
-        <v>-0.01673041897015304</v>
+        <v>0.07230973215273329</v>
       </c>
       <c r="AD6">
-        <v>20.5</v>
+        <v>16.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>20.5</v>
+        <v>16.3</v>
       </c>
       <c r="AG6">
-        <v>17</v>
+        <v>14.77</v>
       </c>
       <c r="AH6">
-        <v>0.4399141630901288</v>
+        <v>0.4604519774011299</v>
       </c>
       <c r="AI6">
-        <v>0.6065088757396451</v>
+        <v>0.5582191780821918</v>
       </c>
       <c r="AJ6">
-        <v>0.394431554524362</v>
+        <v>0.4360791260702687</v>
       </c>
       <c r="AK6">
-        <v>0.5610561056105611</v>
+        <v>0.533791109504879</v>
       </c>
       <c r="AL6">
-        <v>3.95</v>
+        <v>4.48</v>
       </c>
       <c r="AM6">
-        <v>3.906</v>
+        <v>4.187</v>
       </c>
       <c r="AN6">
-        <v>3.528399311531842</v>
+        <v>2.315340909090909</v>
       </c>
       <c r="AO6">
-        <v>1.470886075949367</v>
+        <v>1.558035714285714</v>
       </c>
       <c r="AP6">
-        <v>2.925989672977625</v>
+        <v>2.098011363636364</v>
       </c>
       <c r="AQ6">
-        <v>1.487455197132616</v>
+        <v>1.667064724146167</v>
       </c>
     </row>
     <row r="7">
@@ -1210,7 +1234,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lider Faktoring A.S. (IBSE:LIDFA)</t>
+          <t>Prizma Pres Matbaacilik Yayincilik Sanayi ve Ticaret A.S. (IBSE:PRZMA)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1219,28 +1243,28 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.187</v>
+        <v>0.335</v>
       </c>
       <c r="E7">
-        <v>0.399</v>
+        <v>1.737</v>
       </c>
       <c r="G7">
-        <v>0.003408071748878924</v>
+        <v>0.007655502392344499</v>
       </c>
       <c r="H7">
-        <v>0.003408071748878924</v>
+        <v>0.007655502392344499</v>
       </c>
       <c r="I7">
-        <v>0.1502242152466368</v>
+        <v>0.1186602870813397</v>
       </c>
       <c r="J7">
-        <v>0.1107837853394101</v>
+        <v>0.07710483770675289</v>
       </c>
       <c r="K7">
-        <v>6.32</v>
+        <v>0.475</v>
       </c>
       <c r="L7">
-        <v>0.2834080717488789</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1264,70 +1288,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>2.26</v>
+        <v>0.145</v>
       </c>
       <c r="V7">
-        <v>0.04913043478260869</v>
+        <v>0.004277286135693215</v>
       </c>
       <c r="W7">
-        <v>0.2821428571428572</v>
+        <v>0.1690391459074733</v>
       </c>
       <c r="X7">
-        <v>0.1023694843077783</v>
+        <v>0.07295643199552485</v>
       </c>
       <c r="Y7">
-        <v>0.1797733728350789</v>
+        <v>0.09608271391194845</v>
       </c>
       <c r="Z7">
-        <v>0.1854161470025776</v>
+        <v>0.5964611872146118</v>
       </c>
       <c r="AA7">
-        <v>0.02054110262799405</v>
+        <v>0.0459900430385598</v>
       </c>
       <c r="AB7">
-        <v>0.1050071188420382</v>
+        <v>0.07325080843068189</v>
       </c>
       <c r="AC7">
-        <v>-0.08446601621404416</v>
+        <v>-0.02726076539212209</v>
       </c>
       <c r="AD7">
-        <v>80.7</v>
+        <v>0.499</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>80.7</v>
+        <v>0.499</v>
       </c>
       <c r="AG7">
-        <v>78.44</v>
+        <v>0.354</v>
       </c>
       <c r="AH7">
-        <v>0.6369376479873717</v>
+        <v>0.01450623564638507</v>
       </c>
       <c r="AI7">
-        <v>0.8061938061938063</v>
+        <v>0.1147390204644746</v>
       </c>
       <c r="AJ7">
-        <v>0.6303439408550305</v>
+        <v>0.01033455946750744</v>
       </c>
       <c r="AK7">
-        <v>0.8017170891251022</v>
+        <v>0.08420551855375832</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="AM7">
-        <v>-5.14</v>
+        <v>-0.8109999999999999</v>
       </c>
       <c r="AN7">
-        <v>23.66568914956012</v>
+        <v>1.98804780876494</v>
+      </c>
+      <c r="AO7">
+        <v>1.823529411764706</v>
       </c>
       <c r="AP7">
-        <v>23.00293255131965</v>
+        <v>1.410358565737052</v>
       </c>
       <c r="AQ7">
-        <v>-0.6517509727626459</v>
+        <v>-0.3057953144266338</v>
       </c>
     </row>
     <row r="8">
@@ -1338,7 +1365,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>QNB Finans Finansal Kiralama AS (IBSE:QNBFL)</t>
+          <t>Lider Faktoring A.S. (IBSE:LIDFA)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1347,28 +1374,28 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.139</v>
+        <v>0.281</v>
       </c>
       <c r="E8">
-        <v>0.311</v>
+        <v>0.82</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.1398280802292264</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.1398280802292264</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>0.2673352435530086</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>0.1900824735528996</v>
       </c>
       <c r="K8">
-        <v>19.3</v>
+        <v>18.7</v>
       </c>
       <c r="L8">
-        <v>8.247863247863249</v>
+        <v>0.5358166189111748</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1392,61 +1419,70 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>22.3</v>
+        <v>2.66</v>
       </c>
       <c r="V8">
-        <v>0.02914651679519017</v>
+        <v>0.03783783783783784</v>
       </c>
       <c r="W8">
-        <v>0.146991622239147</v>
+        <v>0.9639175257731959</v>
       </c>
       <c r="X8">
-        <v>0.08311398594257742</v>
+        <v>0.103111133281896</v>
       </c>
       <c r="Y8">
-        <v>0.06387763629656958</v>
+        <v>0.8608063924913</v>
       </c>
       <c r="Z8">
-        <v>0.002526452170157633</v>
+        <v>0.35670482420278</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>0.06780333531271666</v>
       </c>
       <c r="AB8">
-        <v>0.09239581247513468</v>
+        <v>0.09772224326477098</v>
       </c>
       <c r="AC8">
-        <v>-0.09239581247513468</v>
+        <v>-0.02991890795205432</v>
       </c>
       <c r="AD8">
-        <v>634.7</v>
+        <v>84.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>634.7</v>
+        <v>84.7</v>
       </c>
       <c r="AG8">
-        <v>612.4000000000001</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="AH8">
-        <v>0.4534219174167738</v>
+        <v>0.5464516129032259</v>
       </c>
       <c r="AI8">
-        <v>0.8853396568559073</v>
+        <v>0.7099748533109806</v>
       </c>
       <c r="AJ8">
-        <v>0.4445735027223231</v>
+        <v>0.5385322305369569</v>
       </c>
       <c r="AK8">
-        <v>0.8816585084940973</v>
+        <v>0.7033607681755829</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="AN8">
+        <v>9.0491452991453</v>
+      </c>
+      <c r="AP8">
+        <v>8.764957264957266</v>
+      </c>
+      <c r="AQ8">
+        <v>-0.5488235294117647</v>
       </c>
     </row>
     <row r="9">
@@ -1457,7 +1493,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Seker Finansal Kiralama A.S. (IBSE:SEKFK)</t>
+          <t>QNB Finans Finansal Kiralama AS (IBSE:QNBFL)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1465,8 +1501,11 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D9">
+        <v>0.873</v>
+      </c>
       <c r="E9">
-        <v>0.608</v>
+        <v>0.458</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1481,94 +1520,88 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>5.22</v>
+        <v>27.5</v>
       </c>
       <c r="L9">
-        <v>3.48</v>
+        <v>1.175213675213675</v>
       </c>
       <c r="M9">
-        <v>0.209</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.006551724137931035</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.04003831417624521</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>0.209</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.006551724137931035</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.04003831417624521</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>2.67</v>
+        <v>45</v>
       </c>
       <c r="V9">
-        <v>0.08369905956112852</v>
+        <v>0.01290766715428965</v>
       </c>
       <c r="W9">
-        <v>0.3527027027027027</v>
+        <v>0.3345498783454988</v>
       </c>
       <c r="X9">
-        <v>0.1008266624988901</v>
+        <v>0.0779964981975953</v>
       </c>
       <c r="Y9">
-        <v>0.2518760402038125</v>
+        <v>0.2565533801479035</v>
       </c>
       <c r="Z9">
-        <v>0.01634699215344377</v>
+        <v>0.03368845378635185</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.1025556171441484</v>
+        <v>0.0806814871428552</v>
       </c>
       <c r="AC9">
-        <v>-0.1025556171441484</v>
+        <v>-0.0806814871428552</v>
       </c>
       <c r="AD9">
-        <v>53.6</v>
+        <v>744.8</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>53.6</v>
+        <v>744.8</v>
       </c>
       <c r="AG9">
-        <v>50.93</v>
+        <v>699.8</v>
       </c>
       <c r="AH9">
-        <v>0.6269005847953216</v>
+        <v>0.1760298740280305</v>
       </c>
       <c r="AI9">
-        <v>0.8145896656534954</v>
+        <v>0.8982151471297637</v>
       </c>
       <c r="AJ9">
-        <v>0.6148738379814077</v>
+        <v>0.1671723083538377</v>
       </c>
       <c r="AK9">
-        <v>0.8067479803579914</v>
+        <v>0.8923743942871717</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-0.133</v>
-      </c>
-      <c r="AQ9">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1588,10 +1621,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.546</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="E10">
-        <v>0.601</v>
+        <v>1.309</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1606,10 +1639,10 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>71.90000000000001</v>
+        <v>125.5</v>
       </c>
       <c r="L10">
-        <v>0.604201680672269</v>
+        <v>0.6004784688995215</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1633,55 +1666,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>585.3</v>
+        <v>847.3</v>
       </c>
       <c r="V10">
-        <v>0.2826443886420706</v>
+        <v>0.3463173383470939</v>
       </c>
       <c r="W10">
-        <v>0.1512092534174553</v>
+        <v>0.4041867954911433</v>
       </c>
       <c r="X10">
-        <v>0.1049173550335042</v>
+        <v>0.1127791817857437</v>
       </c>
       <c r="Y10">
-        <v>0.04629189838395116</v>
+        <v>0.2914076137053997</v>
       </c>
       <c r="Z10">
-        <v>0.0356234096692112</v>
+        <v>0.05966825591686414</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.1059567601790008</v>
+        <v>0.09957261454558899</v>
       </c>
       <c r="AC10">
-        <v>-0.1059567601790008</v>
+        <v>-0.09957261454558899</v>
       </c>
       <c r="AD10">
-        <v>3886.3</v>
+        <v>3881.3</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>3886.3</v>
+        <v>3881.3</v>
       </c>
       <c r="AG10">
-        <v>3301</v>
+        <v>3034</v>
       </c>
       <c r="AH10">
-        <v>0.6523811921908311</v>
+        <v>0.6133630430316536</v>
       </c>
       <c r="AI10">
-        <v>0.926015059092642</v>
+        <v>0.9159842352441413</v>
       </c>
       <c r="AJ10">
-        <v>0.6145053799471313</v>
+        <v>0.5535890230996606</v>
       </c>
       <c r="AK10">
-        <v>0.9140246434999307</v>
+        <v>0.8949852507374632</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1707,10 +1740,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.679</v>
-      </c>
-      <c r="E11">
-        <v>0.599</v>
+        <v>1.62</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1725,10 +1755,10 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>14.6</v>
+        <v>33.2</v>
       </c>
       <c r="L11">
-        <v>0.6666666666666667</v>
+        <v>0.5804195804195804</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1752,61 +1782,61 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>6.21</v>
+        <v>35.1</v>
       </c>
       <c r="V11">
-        <v>0.05452151009657594</v>
+        <v>0.1698935140367861</v>
       </c>
       <c r="W11">
-        <v>0.4195402298850575</v>
+        <v>1.060702875399361</v>
       </c>
       <c r="X11">
-        <v>0.1152170717249814</v>
+        <v>0.1166360648491587</v>
       </c>
       <c r="Y11">
-        <v>0.3043231581600761</v>
+        <v>0.9440668105502024</v>
       </c>
       <c r="Z11">
-        <v>0.05202147370421397</v>
+        <v>0.193773501812392</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.1070349630124192</v>
+        <v>0.1005182271436389</v>
       </c>
       <c r="AC11">
-        <v>-0.1070349630124192</v>
+        <v>-0.1005182271436389</v>
       </c>
       <c r="AD11">
-        <v>270.1</v>
+        <v>359.2</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>270.1</v>
+        <v>359.2</v>
       </c>
       <c r="AG11">
-        <v>263.89</v>
+        <v>324.1</v>
       </c>
       <c r="AH11">
-        <v>0.7033854166666668</v>
+        <v>0.6348533050547898</v>
       </c>
       <c r="AI11">
-        <v>0.8961512939615129</v>
+        <v>0.8686819830713421</v>
       </c>
       <c r="AJ11">
-        <v>0.698509754096191</v>
+        <v>0.6107028452986621</v>
       </c>
       <c r="AK11">
-        <v>0.8939665977844777</v>
+        <v>0.8565010570824524</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-0.465</v>
+        <v>-3.37</v>
       </c>
       <c r="AQ11">
         <v>-0</v>
@@ -1820,7 +1850,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vakif Finansal Kiralama A.S. (IBSE:VAKFN)</t>
+          <t>Seker Finansal Kiralama A.S. (IBSE:SEKFK)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1828,11 +1858,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D12">
-        <v>0.608</v>
-      </c>
       <c r="E12">
-        <v>0.635</v>
+        <v>0.6920000000000001</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1847,91 +1874,91 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>18.8</v>
+        <v>5.47</v>
       </c>
       <c r="L12">
-        <v>1.413533834586466</v>
+        <v>0.6222980659840729</v>
       </c>
       <c r="M12">
-        <v>0.068</v>
+        <v>0.388</v>
       </c>
       <c r="N12">
-        <v>0.0003992953611274222</v>
+        <v>0.01603305785123967</v>
       </c>
       <c r="O12">
-        <v>0.003617021276595745</v>
+        <v>0.07093235831809873</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>0.388</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.01603305785123967</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0.07093235831809873</v>
       </c>
       <c r="S12">
-        <v>0.068</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>62.8</v>
+        <v>2.67</v>
       </c>
       <c r="V12">
-        <v>0.368761009982384</v>
+        <v>0.1103305785123967</v>
       </c>
       <c r="W12">
-        <v>0.4008528784648188</v>
+        <v>0.4483606557377049</v>
       </c>
       <c r="X12">
-        <v>0.1208356444596767</v>
+        <v>0.1281796103146453</v>
       </c>
       <c r="Y12">
-        <v>0.2800172340051421</v>
+        <v>0.3201810454230597</v>
       </c>
       <c r="Z12">
-        <v>0.03049060064190738</v>
+        <v>0.1392364961191193</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.110444734036115</v>
+        <v>0.1041849484559385</v>
       </c>
       <c r="AC12">
-        <v>-0.110444734036115</v>
+        <v>-0.1041849484559385</v>
       </c>
       <c r="AD12">
-        <v>449.8</v>
+        <v>53.1</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>449.8</v>
+        <v>53.1</v>
       </c>
       <c r="AG12">
-        <v>387</v>
+        <v>50.43</v>
       </c>
       <c r="AH12">
-        <v>0.7253668763102725</v>
+        <v>0.6869340232858991</v>
       </c>
       <c r="AI12">
-        <v>0.8913991280221958</v>
+        <v>0.7937219730941704</v>
       </c>
       <c r="AJ12">
-        <v>0.6944195226987261</v>
+        <v>0.6757336191879941</v>
       </c>
       <c r="AK12">
-        <v>0.8759619737437755</v>
+        <v>0.7851471275105091</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-3.96</v>
+        <v>-0.148</v>
       </c>
       <c r="AQ12">
         <v>-0</v>
@@ -1945,7 +1972,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Is Finansal Kiralama Anonim Sirketi (IBSE:ISFIN)</t>
+          <t>Vakif Finansal Kiralama A.S. (IBSE:VAKFN)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1954,10 +1981,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.07400000000000001</v>
+        <v>2.218</v>
       </c>
       <c r="E13">
-        <v>0.441</v>
+        <v>0.948</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1972,10 +1999,10 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>37.9</v>
+        <v>49</v>
       </c>
       <c r="L13">
-        <v>0.9844155844155844</v>
+        <v>1.240506329113924</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -1999,61 +2026,64 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>20</v>
+        <v>58.8</v>
       </c>
       <c r="V13">
-        <v>0.0664451827242525</v>
+        <v>0.4063579820317899</v>
       </c>
       <c r="W13">
-        <v>0.1881827209533267</v>
+        <v>0.8941605839416059</v>
       </c>
       <c r="X13">
-        <v>0.1501514296051024</v>
+        <v>0.1959444923918016</v>
       </c>
       <c r="Y13">
-        <v>0.03803129134822428</v>
+        <v>0.6982160915498044</v>
       </c>
       <c r="Z13">
-        <v>0.02523132537858457</v>
+        <v>0.08940697148030782</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.1128072737891261</v>
+        <v>0.1090876445743607</v>
       </c>
       <c r="AC13">
-        <v>-0.1128072737891261</v>
+        <v>-0.1090876445743607</v>
       </c>
       <c r="AD13">
-        <v>1218.8</v>
+        <v>704.5</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>1218.8</v>
+        <v>704.5</v>
       </c>
       <c r="AG13">
-        <v>1198.8</v>
+        <v>645.7</v>
       </c>
       <c r="AH13">
-        <v>0.8019476246874588</v>
+        <v>0.8296043334903438</v>
       </c>
       <c r="AI13">
-        <v>0.8861422131743494</v>
+        <v>0.8879505923871944</v>
       </c>
       <c r="AJ13">
-        <v>0.7993065742098946</v>
+        <v>0.8169281376518218</v>
       </c>
       <c r="AK13">
-        <v>0.8844621513944224</v>
+        <v>0.8789817587802886</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>-18.9</v>
+      </c>
+      <c r="AQ13">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -2064,117 +2094,233 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>Is Finansal Kiralama Anonim Sirketi (IBSE:ISFIN)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.925</v>
+      </c>
+      <c r="E14">
+        <v>0.639</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>58.4</v>
+      </c>
+      <c r="L14">
+        <v>0.6496106785317018</v>
+      </c>
+      <c r="M14">
+        <v>-0</v>
+      </c>
+      <c r="N14">
+        <v>-0</v>
+      </c>
+      <c r="O14">
+        <v>-0</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>-0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>31</v>
+      </c>
+      <c r="V14">
+        <v>0.1172022684310019</v>
+      </c>
+      <c r="W14">
+        <v>0.4016506189821183</v>
+      </c>
+      <c r="X14">
+        <v>0.2104506740797767</v>
+      </c>
+      <c r="Y14">
+        <v>0.1911999449023415</v>
+      </c>
+      <c r="Z14">
+        <v>0.06688037637508361</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.1097540679942813</v>
+      </c>
+      <c r="AC14">
+        <v>-0.1097540679942813</v>
+      </c>
+      <c r="AD14">
+        <v>1439.2</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>1439.2</v>
+      </c>
+      <c r="AG14">
+        <v>1408.2</v>
+      </c>
+      <c r="AH14">
+        <v>0.8447496624992663</v>
+      </c>
+      <c r="AI14">
+        <v>0.8453947368421052</v>
+      </c>
+      <c r="AJ14">
+        <v>0.8418724218329646</v>
+      </c>
+      <c r="AK14">
+        <v>0.8425272226875673</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Türkiye Sinai Kalkinma Bankasi A.S. (IBSE:TSKB)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D14">
-        <v>0.419</v>
-      </c>
-      <c r="E14">
-        <v>0.396</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>159.1</v>
-      </c>
-      <c r="L14">
-        <v>0.6176242236024844</v>
-      </c>
-      <c r="M14">
-        <v>0.014</v>
-      </c>
-      <c r="N14">
-        <v>2.141000152928583e-05</v>
-      </c>
-      <c r="O14">
-        <v>8.799497171590195e-05</v>
-      </c>
-      <c r="P14">
-        <v>0.014</v>
-      </c>
-      <c r="Q14">
-        <v>2.141000152928583e-05</v>
-      </c>
-      <c r="R14">
-        <v>8.799497171590195e-05</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>401.6</v>
-      </c>
-      <c r="V14">
-        <v>0.6141611867257991</v>
-      </c>
-      <c r="W14">
-        <v>0.2116254322958234</v>
-      </c>
-      <c r="X14">
-        <v>0.2315226116346315</v>
-      </c>
-      <c r="Y14">
-        <v>-0.01989717933880816</v>
-      </c>
-      <c r="Z14">
-        <v>0.03989044374557021</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0.1178678942096615</v>
-      </c>
-      <c r="AC14">
-        <v>-0.1178678942096615</v>
-      </c>
-      <c r="AD14">
-        <v>5203.2</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>5203.2</v>
-      </c>
-      <c r="AG14">
-        <v>4801.599999999999</v>
-      </c>
-      <c r="AH14">
-        <v>0.8883577196906319</v>
-      </c>
-      <c r="AI14">
-        <v>0.9084274665223389</v>
-      </c>
-      <c r="AJ14">
-        <v>0.8801393089542664</v>
-      </c>
-      <c r="AK14">
-        <v>0.9015226901485139</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
+      <c r="D15">
+        <v>0.652</v>
+      </c>
+      <c r="E15">
+        <v>0.632</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>231.5</v>
+      </c>
+      <c r="L15">
+        <v>0.6191495052152982</v>
+      </c>
+      <c r="M15">
+        <v>-0</v>
+      </c>
+      <c r="N15">
+        <v>-0</v>
+      </c>
+      <c r="O15">
+        <v>-0</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>-0</v>
+      </c>
+      <c r="R15">
+        <v>-0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>570.9</v>
+      </c>
+      <c r="V15">
+        <v>0.920509513060303</v>
+      </c>
+      <c r="W15">
+        <v>0.4771228359439407</v>
+      </c>
+      <c r="X15">
+        <v>0.2826706681678742</v>
+      </c>
+      <c r="Y15">
+        <v>0.1944521677760665</v>
+      </c>
+      <c r="Z15">
+        <v>0.06740167359491216</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.1136359841180625</v>
+      </c>
+      <c r="AC15">
+        <v>-0.1136359841180625</v>
+      </c>
+      <c r="AD15">
+        <v>5142.4</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>5142.4</v>
+      </c>
+      <c r="AG15">
+        <v>4571.5</v>
+      </c>
+      <c r="AH15">
+        <v>0.8923749696317634</v>
+      </c>
+      <c r="AI15">
+        <v>0.8801410306878669</v>
+      </c>
+      <c r="AJ15">
+        <v>0.8805400928404954</v>
+      </c>
+      <c r="AK15">
+        <v>0.8671611214385978</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
         <v>0</v>
       </c>
     </row>
